--- a/patient_import_template.xlsx
+++ b/patient_import_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
   <si>
     <t>First Name</t>
   </si>
@@ -115,22 +115,43 @@
     <t>Scheme Type: Family, Individual, Corporate, Executive, VIP, VVIP</t>
   </si>
   <si>
-    <t>Vip</t>
-  </si>
-  <si>
-    <t>Bertha C</t>
-  </si>
-  <si>
-    <t>Botha</t>
-  </si>
-  <si>
-    <t>BOX 1785 BT</t>
-  </si>
-  <si>
-    <t>Masm Vip</t>
-  </si>
-  <si>
-    <t>MASM 900010963</t>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Exe</t>
+  </si>
+  <si>
+    <t>Masm Exe</t>
+  </si>
+  <si>
+    <t>Bwanali</t>
+  </si>
+  <si>
+    <t>Christabel</t>
+  </si>
+  <si>
+    <t>Box 1131 Blantyre</t>
+  </si>
+  <si>
+    <t>Masm 800050617</t>
+  </si>
+  <si>
+    <t>Masm 800050617-1</t>
+  </si>
+  <si>
+    <t>Masm 800050617-2</t>
+  </si>
+  <si>
+    <t>Masm 800050617-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trevor </t>
+  </si>
+  <si>
+    <t>Tracy</t>
+  </si>
+  <si>
+    <t>Precious</t>
   </si>
 </sst>
 </file>
@@ -209,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -220,9 +241,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -527,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -584,56 +602,169 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="6"/>
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="5"/>
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="2">
-        <v>888460430</v>
+        <v>886535399</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="4" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="E3" s="2"/>
+      <c r="G3" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="2"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="K3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="G4" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+      <c r="K4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/patient_import_template.xlsx
+++ b/patient_import_template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2150" windowHeight="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="1710" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Patients Template" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>First Name</t>
   </si>
@@ -124,34 +124,28 @@
     <t>Masm Exe</t>
   </si>
   <si>
-    <t>Bwanali</t>
-  </si>
-  <si>
-    <t>Christabel</t>
-  </si>
-  <si>
-    <t>Box 1131 Blantyre</t>
-  </si>
-  <si>
-    <t>Masm 800050617</t>
-  </si>
-  <si>
-    <t>Masm 800050617-1</t>
-  </si>
-  <si>
-    <t>Masm 800050617-2</t>
-  </si>
-  <si>
-    <t>Masm 800050617-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trevor </t>
-  </si>
-  <si>
-    <t>Tracy</t>
-  </si>
-  <si>
-    <t>Precious</t>
+    <t>Flossie</t>
+  </si>
+  <si>
+    <t>Bottomani</t>
+  </si>
+  <si>
+    <t>BOX 505 BT</t>
+  </si>
+  <si>
+    <t>Pempho</t>
+  </si>
+  <si>
+    <t>Masm 800026100-1</t>
+  </si>
+  <si>
+    <t>Masm 800026100-2</t>
+  </si>
+  <si>
+    <t>Mafuno</t>
+  </si>
+  <si>
+    <t>Masm 800026100-3</t>
   </si>
 </sst>
 </file>
@@ -549,7 +543,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="7" width="25" customWidth="1"/>
@@ -603,17 +597,17 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="2">
-        <v>886535399</v>
+        <v>999571211</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>36</v>
@@ -625,15 +619,15 @@
         <v>32</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4" t="s">
@@ -650,19 +644,19 @@
         <v>32</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -679,31 +673,17 @@
         <v>32</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>

--- a/patient_import_template.xlsx
+++ b/patient_import_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>First Name</t>
   </si>
@@ -115,37 +115,22 @@
     <t>Scheme Type: Family, Individual, Corporate, Executive, VIP, VVIP</t>
   </si>
   <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Exe</t>
-  </si>
-  <si>
-    <t>Masm Exe</t>
-  </si>
-  <si>
-    <t>Flossie</t>
-  </si>
-  <si>
-    <t>Bottomani</t>
-  </si>
-  <si>
-    <t>BOX 505 BT</t>
-  </si>
-  <si>
-    <t>Pempho</t>
-  </si>
-  <si>
-    <t>Masm 800026100-1</t>
-  </si>
-  <si>
-    <t>Masm 800026100-2</t>
-  </si>
-  <si>
-    <t>Mafuno</t>
-  </si>
-  <si>
-    <t>Masm 800026100-3</t>
+    <t>Vip</t>
+  </si>
+  <si>
+    <t>Masm Vip</t>
+  </si>
+  <si>
+    <t>Masm 903212355</t>
+  </si>
+  <si>
+    <t>Eileen Mtd</t>
+  </si>
+  <si>
+    <t>Bouton</t>
+  </si>
+  <si>
+    <t>BOX 30376  BT 3</t>
   </si>
 </sst>
 </file>
@@ -607,74 +592,46 @@
         <v>13</v>
       </c>
       <c r="E2" s="2">
-        <v>999571211</v>
+        <v>888935053</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>36</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="D3" s="4"/>
       <c r="E3" s="2"/>
-      <c r="G3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="G3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="4"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="G4" s="4"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>

--- a/patient_import_template.xlsx
+++ b/patient_import_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <si>
     <t>First Name</t>
   </si>
@@ -115,22 +115,34 @@
     <t>Scheme Type: Family, Individual, Corporate, Executive, VIP, VVIP</t>
   </si>
   <si>
-    <t>Vip</t>
-  </si>
-  <si>
-    <t>Masm Vip</t>
-  </si>
-  <si>
-    <t>Masm 903212355</t>
-  </si>
-  <si>
-    <t>Eileen Mtd</t>
-  </si>
-  <si>
-    <t>Bouton</t>
-  </si>
-  <si>
-    <t>BOX 30376  BT 3</t>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Exe</t>
+  </si>
+  <si>
+    <t>Masm Exe</t>
+  </si>
+  <si>
+    <t>Fred Pemphero</t>
+  </si>
+  <si>
+    <t>Balakasi</t>
+  </si>
+  <si>
+    <t>Masm 2600526</t>
+  </si>
+  <si>
+    <t>Tamanda</t>
+  </si>
+  <si>
+    <t>Masm 2600526-1</t>
+  </si>
+  <si>
+    <t>Masm 2600526-2</t>
+  </si>
+  <si>
+    <t>Mwayi Ken</t>
   </si>
 </sst>
 </file>
@@ -589,54 +601,77 @@
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="2">
+        <v>9953133554</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="K2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2">
-        <v>888935053</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="E3" s="2">
+        <v>9953133554</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="K3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M3" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="2"/>
-      <c r="G3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="4"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+      <c r="K4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="D5" s="4"/>
       <c r="G5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
